--- a/www/download/COUNTRY.BEL.EXI382.xlsx
+++ b/www/download/COUNTRY.BEL.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3009509202454</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.30071595092025</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.30071595092025</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.30071595092025</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.30071595092025</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.30071595092025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.891</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.791</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.801</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3.894</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.033</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.114</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.162</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.307</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.379</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.458</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.449</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.479</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.518</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.556</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.542</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4.449</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.563</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4.624</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4.74</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>4.818</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4.855</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4.834</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.092</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3.096</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.204</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.189</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.328</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.412</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.475</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.473</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.471</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.509</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.566</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.608</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.673</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.742</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.728</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.752</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.782</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.807</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.718</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.822</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>3.881</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.993</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>4.049</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>4.06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4.042</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7894.787</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5446.3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5504.5</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5696.2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5652.2</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>6379.5</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6558.2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6621.4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6585.4</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6562.8</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6604.7</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6667.2</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6782.2</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6913.8</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7010</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>6914.6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>6987.1</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7099.3</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7163.9</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7150.906</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>7059.729</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7248.264</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>7357.461</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7493.553</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>7632.884</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>7779.707</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>7764.48</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5987.842</t>
+          <t>22940755728.5398</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3496.1</t>
+          <t>14362143030.6067</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3409.7</t>
+          <t>15534983165.3745</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3711.7</t>
+          <t>15947811370.1489</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>16232930918.8221</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3250.1</t>
+          <t>17983768496.9914</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4977.2</t>
+          <t>19622050520.6122</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5052.1</t>
+          <t>17619250976.3742</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5025.4</t>
+          <t>16227166326.3221</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5024.4</t>
+          <t>18106427947.7261</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5081.2</t>
+          <t>18722480707.9182</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5147.5</t>
+          <t>18657258588.9242</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5214.6</t>
+          <t>17207635107.9906</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>21272187460.2408</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5402.8</t>
+          <t>18261554061.053</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5298.7</t>
+          <t>19202502000.5342</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5348.2</t>
+          <t>22151426456.7908</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5410.5</t>
+          <t>21383647968.6485</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5453.9</t>
+          <t>24735030604.9863</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5446.137</t>
+          <t>20785746211.4736</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5340.488</t>
+          <t>19818614643.7126</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5482.491</t>
+          <t>21365703696.848</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>5579.218</t>
+          <t>18334982395.9567</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5692.661</t>
+          <t>20963789151.9294</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>5798.441</t>
+          <t>19010318769.0764</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>5896.819</t>
+          <t>21296009431.8871</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5907.796</t>
+          <t>22419555602.512</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16527215322.8516</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8195537499.49487</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10955316320.4011</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9231960897.08163</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10680321292.5516</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>9546605129.57443</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10689015537.4506</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>10807449360.3777</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>10480712980.9023</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>11958062455.3204</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>13060476666.9074</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>13792537064.1104</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>12291014694.3356</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>11162049386.1618</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>12226184549.9706</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>11401187835.1243</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>9816484638.0919</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>12538295484.0354</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>11203821000.0318</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>9756101857.02588</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>10331064151.6905</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>12513875027.5579</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>11848537552.5843</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13875974073.013</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>11697600588.4083</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13994981012.4459</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>14031523493.5452</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>27624822.8429843</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>120865253.11514</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6198535.85846957</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6136806.98537602</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>82224134.5718697</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5815705.034201</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6233027.88908832</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>16488965.9482111</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6032299.78902046</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6419970.85443853</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6110679.55868462</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>20643524.843358</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4761316.15577679</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5705602.83583409</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5057841.87002925</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4525309.72683836</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4651188.14051406</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4650558.90710789</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5329946.28788175</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4534192.38201831</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4165747.09020519</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>73269431.9076962</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>4311121.92925311</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4110285.05677634</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3639796.52127792</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3900864.93694594</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4022288.96310469</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11862.4665187145</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21249.2862349758</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>23682.7319675376</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24471.7143760501</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>26048.1007034894</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>33000.757350839</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>33786.5804731424</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>32885.9515260668</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>29648.4099404755</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>28757.9137205226</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>30890.9884868874</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>33172.2312627416</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>35061.0336548206</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>35745.6814345954</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>36166.6128246108</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>40778.8832475328</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>42741.1081059648</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>47672.2356931671</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>47072.7569122625</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>48399.1214309005</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>51424.9594838512</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>48110.8414080619</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>51164.419031722</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>49864.781671571</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>53512.4074132721</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>52041.1437083298</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>51003.6618793426</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>85514.0216525486</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>109138.965134249</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>128577.214798974</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>135698.98636073</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>145695.34121925</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>192944.49768293</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>211383.473826694</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>183991.437042651</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>155663.661764324</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>169737.292664786</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>188156.658206267</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>200571.311741477</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>191657.128130147</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>238067.888657068</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>204806.051631641</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>248352.866203677</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>298253.689796818</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>317789.857828066</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>359077.926011796</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>312331.586998865</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>336404.081051603</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>330558.155167285</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>299906.969097284</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>333501.489982084</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>322222.445792918</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>343386.588766883</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>354916.365707967</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.637698070138751</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.573414190318023</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.688762980430717</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.597951070051325</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.668174776495778</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.65955436975891</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.534363105511285</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.532535399284622</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.520509720172988</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.579831597403598</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.610948349773882</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.626790924971104</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.575738852350177</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.523474604350353</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.55809598833397</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.535250179487667</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.455181748133467</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.568482015207628</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.513210716238211</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.441771202368013</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.483065023386283</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.561887006715459</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.529121844576704</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.589746897556414</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.504305115137311</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.578647578603998</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.578962577309486</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4050.87643338368</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2650.56193386103</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3538.08174667361</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2881.56592080752</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3349.007962293</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2868.48506041654</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3133.04673255285</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3110.41540332031</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3017.94315275925</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3445.33319560775</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3722.31215746828</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3868.00635596936</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>3406.78937145618</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3039.11168213958</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3266.84957915055</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3057.93043534024</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2616.12468035351</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>3315.25528398698</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2940.32673735918</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2562.80807581515</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2778.86060703003</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3274.48009199864</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>3053.04175324336</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>3475.16831843774</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2889.21343211303</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>3447.00936488395</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3471.72852742144</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>23683502628.9613</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>11552660355.793</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>13560723344.3446</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>13456129194.6914</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>14146317190.9031</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>13681433431.2295</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>15331547435.8612</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>16417135728.9384</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>15410012515.1451</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>18125283288.4896</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>18257494698.0115</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>18112819131.6897</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>15420319123.451</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>15807813621.7552</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>16305409258.0321</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>16435053417.2866</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>14613325389.5412</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>16243901184.1484</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>17447562096.5917</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>14929970810.3727</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>15411728365.3495</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>17577720208.4777</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>15134668436.9763</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>17670236164.5904</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>15994524820.6987</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>18610839298.896</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>19361592180.3754</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>18881656263.0195</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9385615938.54795</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>11234155115.0677</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10945291251.6593</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>11053255184.4098</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10826153708.8251</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11648814746.4146</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12320437422.3797</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>11857602862.8811</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>14037235771.8201</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>14735123188.2422</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>14445981950.4646</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>12534123381.2579</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>13086567815.2702</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>12934415611.5055</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>13728822798.1814</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>12098821999.9195</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13473205815.2121</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>14903455191.3801</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>11812406731.806</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>12093616279.0164</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>13313932931.491</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>11713810014.3916</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14310515213.7556</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>12878970270.357</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15064789597.5298</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15599154859.3162</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4801846365.94181</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2167044417.24501</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2326568229.27692</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2510837943.03205</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3093062006.4933</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2855279722.40442</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3682732689.44663</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>4096698306.55872</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3552409652.26399</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>4088047516.66953</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3522371509.76932</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3666837181.22515</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2886195742.19309</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2721245806.48498</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3370993646.52667</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2706230619.10519</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2514503389.62178</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2770695368.9363</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2544106905.21157</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3117564078.56671</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>3318112086.33311</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>4263787276.98663</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>3420858422.58469</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>3359720950.83483</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>3115554550.3417</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3546049701.36618</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3762437321.05929</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>1467.64034944436</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>1130.69210866833</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>1101.18201782718</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1158.53049503723</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>1111.28531560529</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>976.56320423066</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>1458.86215083392</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>1454.00909457209</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>1447.07440681855</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1447.62014521087</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>1448.17168751977</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1443.57507431722</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>1445.36836853522</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>1448.21389675503</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>1443.63393453611</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>1421.17262096358</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1425.31247501509</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>1430.59227921832</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1431.31954650471</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>1430.63327072384</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>1436.49024290785</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>1434.59227455616</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>1437.61066919754</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>1425.69858415274</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1432.16831957501</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1452.40574246855</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1461.72763146666</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1614.0488044933</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1436.7152052345</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>1448.28584208166</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>1456.977695928</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>1451.40333307565</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1581.78572314079</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1594.23390135402</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>1587.71340878579</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>1582.1921099418</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>1577.52031152294</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>1572.47273939345</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>1564.9969485002</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>1574.65580088722</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1578.99785319543</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>1572.48928867896</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1554.22688754529</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>1559.96874302277</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>1571.3020960147</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>1572.51355444865</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1574.263310246</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1586.73660848701</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>1588.3847829064</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1591.25293478331</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1581.054322648</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1584.23034571476</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>1602.37417213562</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>1606.24754514494</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>114656.620597968</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>126417.979193253</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>139138.086527445</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>141644.525645627</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>153489.150543614</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>183747.086885877</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>188988.692621108</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>188978.654043347</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>180080.938325782</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>186052.803348418</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>203791.101571794</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>218274.67628877</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>218806.300806213</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>220460.500999265</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>203451.171761572</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>239836.534270067</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>251077.373085584</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>270278.313087074</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>264745.584954576</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>283065.053329769</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>306792.692031867</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>324255.06599126</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>353187.804859118</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>358646.124685501</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>369146.078941729</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>382749.722421426</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>396167.029497967</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9497080924.0194</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6322760296.87222</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7432419623.62214</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>7814655417.60907</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>7657224665.85138</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>8944896617.21382</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9473798485.00333</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7096416410.81654</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>6185995865.66469</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6616802310.24347</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>7245819903.22444</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6926775664.51702</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6051102344.2522</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7588858488.7222</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6115012939.07974</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6914418546.40919</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7754243204.83449</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>7865052897.76173</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>8872534739.09369</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>7694755363.51707</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>7272339526.39889</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>8272715521.45973</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>7850361476.35587</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>9089841673.19082</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>8218867078.00367</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>9352623497.35568</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>9592941996.89366</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>103566.986109599</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>117294.734948807</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>127816.373623395</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>130666.815784176</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>140955.537690921</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>174164.471308048</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>176389.526722011</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>169138.038848254</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>160420.518968939</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>167085.766944973</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>187428.120179476</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>201097.350782961</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>200245.514594375</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>217377.690653593</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>193241.467031119</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>231757.866602213</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>251563.558142067</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>269960.323049797</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>260646.637804041</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>278754.65339373</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>299066.868846901</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>317541.588955055</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>347139.713865103</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>360234.237285622</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>365308.494442446</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>379102.822139977</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>393037.419927736</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7894.787</t>
+          <t>26898014626.6554</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5446.3</t>
+          <t>16022142617.9683</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5504.5</t>
+          <t>18873857374.8153</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5696.2</t>
+          <t>19202602511.1757</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5652.2</t>
+          <t>19504327123.503</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6379.5</t>
+          <t>21139677525.2964</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6558.2</t>
+          <t>22773365187.9821</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6621.4</t>
+          <t>20193551550.1341</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6585.4</t>
+          <t>18256142402.9937</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6562.8</t>
+          <t>21263723796.1416</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6604.7</t>
+          <t>22766596402.2073</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6667.2</t>
+          <t>22483751339.7163</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6782.2</t>
+          <t>19166498415.452</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6913.8</t>
+          <t>22974205786.2375</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>20917641362.3125</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>6914.6</t>
+          <t>22353355950.547</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>6987.1</t>
+          <t>22423633391.383</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>7099.3</t>
+          <t>24074283236.5268</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>7163.9</t>
+          <t>25850547860.4233</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7150.906</t>
+          <t>22166504399.398</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>7059.729</t>
+          <t>21937252094.3875</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>7248.264</t>
+          <t>25138427639.5545</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>7357.461</t>
+          <t>22402461114.0622</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7493.553</t>
+          <t>26917919882.4482</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>7632.884</t>
+          <t>23863145515.7725</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>7779.707</t>
+          <t>27609562755.5922</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>7764.48</t>
+          <t>28649600437.2465</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5987.842</t>
+          <t>11089.6344883691</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3496.1</t>
+          <t>9123.24424444607</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3409.7</t>
+          <t>11321.7129040501</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3711.7</t>
+          <t>10977.7098614515</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>12533.6128526935</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3250.1</t>
+          <t>9582.61557782902</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4977.2</t>
+          <t>12599.1658990962</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5052.1</t>
+          <t>19840.6151950935</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5025.4</t>
+          <t>19660.4193568424</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5024.4</t>
+          <t>18967.0364034447</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5081.2</t>
+          <t>16362.9813923176</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5147.5</t>
+          <t>17177.3255058097</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5214.6</t>
+          <t>18560.7862118381</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>3082.81034567173</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5402.8</t>
+          <t>10209.7047304531</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5298.7</t>
+          <t>8078.66766785469</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5348.2</t>
+          <t>-486.185056482704</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5410.5</t>
+          <t>317.990037277018</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5453.9</t>
+          <t>4098.94715053461</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5446.137</t>
+          <t>4310.39993603949</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>5340.488</t>
+          <t>7725.82318496647</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>5482.491</t>
+          <t>6713.47703620524</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>5579.218</t>
+          <t>6048.09099401561</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5692.661</t>
+          <t>-1588.11260012117</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>5798.441</t>
+          <t>3837.58449928326</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>5896.819</t>
+          <t>3646.90028144924</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>5907.796</t>
+          <t>3129.60957023154</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18371.013</t>
+          <t>-17400933702.636</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12127.386</t>
+          <t>-9699382321.0961</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13321.565</t>
+          <t>-11441437751.1931</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13636.563</t>
+          <t>-11387947093.5667</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13737.915</t>
+          <t>-11847102457.6516</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15241.983</t>
+          <t>-12194780908.0825</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16482.958</t>
+          <t>-13299566702.9787</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14869.372</t>
+          <t>-13097135139.3175</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13845.315</t>
+          <t>-12070146537.329</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>15407.266</t>
+          <t>-14646921485.8982</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15838.775</t>
+          <t>-15520776498.9828</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>15740.381</t>
+          <t>-15556975675.1992</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>14680.662</t>
+          <t>-13115396071.1998</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>18012.813</t>
+          <t>-15385347297.5153</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>15386.918</t>
+          <t>-14802628423.2328</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>16218.829</t>
+          <t>-15438937404.1378</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>18514.948</t>
+          <t>-14669390186.5485</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>17908.03</t>
+          <t>-16209230338.765</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>20560.832</t>
+          <t>-16978013121.3296</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>17340.21</t>
+          <t>-14471749035.881</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>16447.015</t>
+          <t>-14664912567.9886</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>17727.206</t>
+          <t>-16865712118.0948</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>15519.37</t>
+          <t>-14552099637.7063</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17496.326</t>
+          <t>-17828078209.2574</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>16025.575</t>
+          <t>-15644278437.7689</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17780.073</t>
+          <t>-18256939258.2365</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>18524.337</t>
+          <t>-19056658440.3529</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>99472.3068996248</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>100255.139556503</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>101435.516842707</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>102811.788898579</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>109662.011832995</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>109695.792386999</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>115891.855997904</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>118775.304787135</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>120773.262977381</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126352.038457171</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>130948.22729647</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>135986.410193678</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>145332.497020301</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>141779.131776503</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>149898.414332477</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>151074.910961838</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>159124.582728618</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>161854.135533234</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>163760.116545921</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>158084.433063664</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>165231.640884965</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>169718.611233124</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>175982.220547222</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>180613.253482251</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>185312.898508414</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>188178.317870587</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>191478.740919625</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3182.331</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2796.3</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2861.4</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2876</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2902.2</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3075.9</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3136.3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3149.2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3090.7</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>3067.7</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3073.8</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3085.7</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>3147.9</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>3194</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>3224.8</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>3153</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>3174.4</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>3207.8</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>3242.6</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>3220.974</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>3029.605</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3109.655</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>3127.966</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>3134.483</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>3157.098</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>3227.466</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3221.828</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>158440.73917837</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>154606.52166269</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>161417.011957709</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>160464.636346243</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>176569.290287449</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>175616.881120787</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>187707.458280077</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>197018.059867612</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>202604.300818084</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>209933.566433836</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>230470.507516846</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>235745.35114065</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>248586.46048159</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>244548.441230792</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>261890.402596481</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>258682.76187317</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>265068.779857778</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>272737.42011345</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>276576.575334175</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>277604.033637769</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>288548.918981303</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>299466.000884003</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>309781.859074384</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>320537.27519245</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>327103.428532982</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>332936.099565425</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>336757.238124152</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>13834.665</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>6800.684</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>9268.04</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>7804.665</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>8875.015</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>8005.335</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8986.486</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>9136.299</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>8978.231</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>10214.913</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>11222.887</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>11797.249</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>10732.519</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>9643.137</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>10482.475</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>9733.068</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>8351.358</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>10547.013</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>9459.078</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>8306.719</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>8645.696</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>10551.254</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>10116.186</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11768.09</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>9989.771</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11832.991</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>11766.75</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-56.72</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-48.59</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-63.21</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-52.44</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-60.07</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-59.4</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-44.61</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-44.7</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-44.03</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-50.81</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-54.72</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-56.37</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-51.41</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-44.84</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-48.46</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-45.56</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-35.96</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-48.7</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-42.34</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-34.44</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-38.23</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-48.04</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-44.85</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-51.63</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-41.96</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-50.17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-49.79</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>33.154</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>156.891</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.933</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6.815</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>106.282</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6.456</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.892</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>20.448</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6.743</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>7.076</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>6.709</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>25.888</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6.408</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>5.551</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>5.024</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>5.135</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>5.847</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>4.966</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>4.559</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>94.898</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>4.893</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>4.552</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>4.036</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>4.316</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>4.373</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>112323.26495192</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>113264.326921936</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>110843.499361768</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>120148.9421424</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>119613.283376382</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>140194.243770706</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>136311.683351252</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>134076.810946505</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>140231.162605799</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>152828.658500472</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>145683.644986947</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>165337.431227235</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>172958.040758043</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>188017.690776724</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>154061.363549412</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>185999.114142035</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>197911.353500105</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>203747.070036603</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>207509.052954585</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>218284.917892445</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>225252.765495387</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>231193.971692049</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>238256.261254326</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>246698.000370044</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>259764.571867325</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>262704.697133339</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>264957.338323238</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5987842006.70153</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3496100000.00102</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3409700000.00038</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3711699999.99968</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3543999999.99785</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3250100000.00079</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4977200000.00014</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5052100000.00061</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5025399999.99944</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5024400000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5081200000.00002</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5147499999.99841</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5214599999.99965</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5319000000.00165</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5402800000.00127</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5298700000.00143</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5348199999.99991</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5410500000.00227</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5453900000.00078</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>5446137009.22275</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>5340488405.64894</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5482491245.91204</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>5579217507.22453</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>5692661412.88035</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>5798440776.84077</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>5896819136.98516</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>5907796488.14366</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7894787320.46918</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5446300000.00109</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5504500000.00004</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5696199999.99943</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5652199999.99782</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6379500000.00024</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6558200000.00022</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6621400000.00076</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6585399999.9998</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6562799999.99999</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6604699999.99968</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6667199999.99852</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6782199999.99948</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6913800000.0014</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7010000000.00171</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6914600000.00112</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6987099999.99979</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>7099300000.00237</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7163900000.00089</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7150906220.16126</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>7059728960.53178</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>7248263614.15663</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>7357460821.22353</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>7493552911.71357</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>7632883629.44109</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>7779707357.70618</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>7764479941.7072</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3182331288.89105</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2796300000.00113</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2861399999.99992</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2875999999.9996</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2902199999.99833</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3075899999.99976</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3136300000.00034</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3149199999.99964</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3090700000.00054</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3067699999.99883</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3073799999.99921</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3085699999.99945</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3147900000.00125</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3194000000.00037</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3224800000.00043</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>3153000000.00041</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3174400000.00002</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3207800000.0008</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3242600000.00012</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3220973788.10631</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>3029604908.15997</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3109655490.45522</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3127965732.40575</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3134483054.71129</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>3157098260.25207</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>3227466428.54815</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3221827855.57013</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4891294.05411481</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3790799.9999987</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3800700.0000002</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3909599.99999952</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3894300.00000092</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4033100.00000071</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4113700.00000012</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4170400.00000033</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4162200.00000003</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4160200.00000143</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4200199.99999957</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4260199.99999871</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4307099.99999883</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4378599.99999992</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4457899.99999987</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4448900.00000057</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4479000.0000005</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4518099.99999895</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4555699.99999948</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4542382.56943422</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>4449212.88307794</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4563292.02606301</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4623690.33884952</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>4739592.31151726</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>4818039.02449383</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4855112.80260933</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4833924.86119354</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4079911.00065386</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3091999.9999987</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3096400.00000028</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3203799.99999948</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3189100.00000091</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3328100.00000075</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3411700.00000003</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3474600.0000003</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3472799.99999998</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3470800.00000147</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3508699.99999958</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3565799.99999867</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3607799.99999881</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3672799.99999985</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3742499.99999991</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3728400.00000058</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3752300.00000054</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3781999.99999899</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3810399.99999946</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3806801.58966752</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3717733.85306004</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3821637.22971967</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3880896.00805397</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3992892.66059232</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>4048714.59421854</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>4060035.68049983</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4041653.42500636</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7894787320.46918</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5446300000.00109</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5504500000.00004</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5696199999.99943</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5652199999.99782</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6379500000.00024</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6558200000.00022</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6621400000.00076</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6585399999.9998</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6562799999.99999</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6604699999.99968</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6667199999.99852</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6782199999.99948</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6913800000.0014</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7010000000.00171</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6914600000.00112</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>6987099999.99979</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7099300000.00237</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7163900000.00089</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7150906220.16126</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>7059728960.53178</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>7248263614.15663</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>7357460821.22353</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>7493552911.71357</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>7632883629.44109</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>7779707357.70618</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>7764479941.7072</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5987842006.70153</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3496100000.00102</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3409700000.00038</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3711699999.99968</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3543999999.99785</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3250100000.00079</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4977200000.00014</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5052100000.00061</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5025399999.99944</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5024400000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5081200000.00002</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5147499999.99841</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5214599999.99965</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5319000000.00165</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5402800000.00127</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5298700000.00143</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5348199999.99991</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5410500000.00227</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5453900000.00078</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>5446137009.22275</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>5340488405.64894</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>5482491245.91204</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>5579217507.22453</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>5692661412.88035</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>5798440776.84077</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>5896819136.98516</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5907796488.14366</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>541281.637415645</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>549377.156701978</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>565606.166957802</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>584172.121840974</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>625426.181230976</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>681964.910268392</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>704730.061919015</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>711235.859337099</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>716145.527920787</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>752539.601914946</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>800051.275246721</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>855685.316430245</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>909410.959564939</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>931953.537321194</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>871549.842671067</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>954339.827259172</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1027453.00748118</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1052720.52674548</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1064186.37229802</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1079554.26433908</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1117252.90688823</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1149979.02456019</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1200405.99476122</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1237328.06558221</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1285847.6659665</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1300161.68776288</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1322556.4860493</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>172806.269142529</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>171610.681531188</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>177814.747913651</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>178729.614164472</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>194092.042918714</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>191364.135608403</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>206175.841604781</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>218393.089654858</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>223416.790602962</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>231207.957562803</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>255490.295363794</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>255247.215088924</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>271420.186247473</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>265932.769357667</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>292420.11075556</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>283766.461550859</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>288284.191040991</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>296215.577721739</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>300898.938191442</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>302816.394501296</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>314015.141556687</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>325194.797857661</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>337803.074531051</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>349246.902140598</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>356728.274200096</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>361787.166312345</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>367667.745740041</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
